--- a/astro-site/public/dl/kit-tareas-bar/07-plantilla-personalizable.xlsx
+++ b/astro-site/public/dl/kit-tareas-bar/07-plantilla-personalizable.xlsx
@@ -1,18 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Por Franja Horaria" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Por Zona" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Por Perfil" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Por Franja Horaria" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Por Zona" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Por Perfil" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Por Franja Horaria'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Por Zona'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Por Perfil'!$4:$4</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -137,7 +141,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -159,68 +163,127 @@
         <color rgb="00E0E0E0"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E0E0E0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E0E0E0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E0E0E0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E0E0E0"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="2" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="33">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="3" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="3" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="11" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="12" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="5" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="5" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="5" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="6" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="6" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="6" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="7" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="7" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="7" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C8E6C9"/>
+          <bgColor rgb="00C8E6C9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -580,15 +643,16 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B9"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="3"/>
-    <col customWidth="1" max="2" min="2" width="80"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -596,6 +660,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -603,9 +668,7 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="B5" t="inlineStr"/>
-    </row>
+    <row r="5"/>
     <row r="6">
       <c r="B6" s="2" t="inlineStr">
         <is>
@@ -634,8 +697,33 @@
         </is>
       </c>
     </row>
+    <row r="10"/>
+    <row r="11">
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Marca con ✓ en la columna «✓ Completada» (desplegable): es la que cuenta el total de tareas completadas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12"/>
+    <row r="13">
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas-bar · info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -644,18 +732,18 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="12"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -672,10 +760,11 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -700,7 +789,7 @@
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Hecha</t>
+          <t>✓ Completada</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
@@ -715,18 +804,16 @@
           <t xml:space="preserve">  Apertura (15:00 - 18:00)</t>
         </is>
       </c>
-      <c r="B5" s="8" t="n"/>
-      <c r="C5" s="8" t="n"/>
-      <c r="D5" s="8" t="n"/>
-      <c r="E5" s="8" t="n"/>
-      <c r="F5" s="8" t="n"/>
-      <c r="G5" s="8" t="n"/>
+      <c r="B5" s="30" t="n"/>
+      <c r="C5" s="30" t="n"/>
+      <c r="D5" s="30" t="n"/>
+      <c r="E5" s="30" t="n"/>
+      <c r="F5" s="30" t="n"/>
+      <c r="G5" s="31" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A6" s="32" t="n">
+        <v>1</v>
       </c>
       <c r="B6" s="10" t="inlineStr"/>
       <c r="C6" s="11" t="inlineStr">
@@ -740,10 +827,8 @@
       <c r="G6" s="15" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A7" s="32" t="n">
+        <v>2</v>
       </c>
       <c r="B7" s="10" t="inlineStr"/>
       <c r="C7" s="11" t="inlineStr">
@@ -757,10 +842,8 @@
       <c r="G7" s="15" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A8" s="32" t="n">
+        <v>3</v>
       </c>
       <c r="B8" s="10" t="inlineStr"/>
       <c r="C8" s="11" t="inlineStr">
@@ -774,10 +857,8 @@
       <c r="G8" s="15" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A9" s="32" t="n">
+        <v>4</v>
       </c>
       <c r="B9" s="10" t="inlineStr"/>
       <c r="C9" s="11" t="inlineStr">
@@ -791,10 +872,8 @@
       <c r="G9" s="15" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A10" s="32" t="n">
+        <v>5</v>
       </c>
       <c r="B10" s="10" t="inlineStr"/>
       <c r="C10" s="11" t="inlineStr">
@@ -807,24 +886,23 @@
       <c r="F10" s="14" t="n"/>
       <c r="G10" s="15" t="n"/>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Servicio Tarde (18:00 - 22:00)</t>
         </is>
       </c>
-      <c r="B12" s="8" t="n"/>
-      <c r="C12" s="8" t="n"/>
-      <c r="D12" s="8" t="n"/>
-      <c r="E12" s="8" t="n"/>
-      <c r="F12" s="8" t="n"/>
-      <c r="G12" s="8" t="n"/>
+      <c r="B12" s="30" t="n"/>
+      <c r="C12" s="30" t="n"/>
+      <c r="D12" s="30" t="n"/>
+      <c r="E12" s="30" t="n"/>
+      <c r="F12" s="30" t="n"/>
+      <c r="G12" s="31" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A13" s="32" t="n">
+        <v>6</v>
       </c>
       <c r="B13" s="10" t="inlineStr"/>
       <c r="C13" s="11" t="inlineStr">
@@ -838,10 +916,8 @@
       <c r="G13" s="15" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A14" s="32" t="n">
+        <v>7</v>
       </c>
       <c r="B14" s="10" t="inlineStr"/>
       <c r="C14" s="11" t="inlineStr">
@@ -855,10 +931,8 @@
       <c r="G14" s="15" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A15" s="32" t="n">
+        <v>8</v>
       </c>
       <c r="B15" s="10" t="inlineStr"/>
       <c r="C15" s="11" t="inlineStr">
@@ -872,10 +946,8 @@
       <c r="G15" s="15" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A16" s="32" t="n">
+        <v>9</v>
       </c>
       <c r="B16" s="10" t="inlineStr"/>
       <c r="C16" s="11" t="inlineStr">
@@ -889,10 +961,8 @@
       <c r="G16" s="15" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A17" s="32" t="n">
+        <v>10</v>
       </c>
       <c r="B17" s="10" t="inlineStr"/>
       <c r="C17" s="11" t="inlineStr">
@@ -905,24 +975,23 @@
       <c r="F17" s="14" t="n"/>
       <c r="G17" s="15" t="n"/>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Servicio Noche (22:00 - 02:00)</t>
         </is>
       </c>
-      <c r="B19" s="8" t="n"/>
-      <c r="C19" s="8" t="n"/>
-      <c r="D19" s="8" t="n"/>
-      <c r="E19" s="8" t="n"/>
-      <c r="F19" s="8" t="n"/>
-      <c r="G19" s="8" t="n"/>
+      <c r="B19" s="30" t="n"/>
+      <c r="C19" s="30" t="n"/>
+      <c r="D19" s="30" t="n"/>
+      <c r="E19" s="30" t="n"/>
+      <c r="F19" s="30" t="n"/>
+      <c r="G19" s="31" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A20" s="32" t="n">
+        <v>11</v>
       </c>
       <c r="B20" s="10" t="inlineStr"/>
       <c r="C20" s="11" t="inlineStr">
@@ -936,10 +1005,8 @@
       <c r="G20" s="15" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A21" s="32" t="n">
+        <v>12</v>
       </c>
       <c r="B21" s="10" t="inlineStr"/>
       <c r="C21" s="11" t="inlineStr">
@@ -953,10 +1020,8 @@
       <c r="G21" s="15" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A22" s="32" t="n">
+        <v>13</v>
       </c>
       <c r="B22" s="10" t="inlineStr"/>
       <c r="C22" s="11" t="inlineStr">
@@ -970,10 +1035,8 @@
       <c r="G22" s="15" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A23" s="32" t="n">
+        <v>14</v>
       </c>
       <c r="B23" s="10" t="inlineStr"/>
       <c r="C23" s="11" t="inlineStr">
@@ -987,10 +1050,8 @@
       <c r="G23" s="15" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A24" s="32" t="n">
+        <v>15</v>
       </c>
       <c r="B24" s="10" t="inlineStr"/>
       <c r="C24" s="11" t="inlineStr">
@@ -1003,24 +1064,23 @@
       <c r="F24" s="14" t="n"/>
       <c r="G24" s="15" t="n"/>
     </row>
+    <row r="25"/>
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Cierre (02:00 - 03:00)</t>
         </is>
       </c>
-      <c r="B26" s="8" t="n"/>
-      <c r="C26" s="8" t="n"/>
-      <c r="D26" s="8" t="n"/>
-      <c r="E26" s="8" t="n"/>
-      <c r="F26" s="8" t="n"/>
-      <c r="G26" s="8" t="n"/>
+      <c r="B26" s="30" t="n"/>
+      <c r="C26" s="30" t="n"/>
+      <c r="D26" s="30" t="n"/>
+      <c r="E26" s="30" t="n"/>
+      <c r="F26" s="30" t="n"/>
+      <c r="G26" s="31" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A27" s="32" t="n">
+        <v>16</v>
       </c>
       <c r="B27" s="10" t="inlineStr"/>
       <c r="C27" s="11" t="inlineStr">
@@ -1034,10 +1094,8 @@
       <c r="G27" s="15" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A28" s="32" t="n">
+        <v>17</v>
       </c>
       <c r="B28" s="10" t="inlineStr"/>
       <c r="C28" s="11" t="inlineStr">
@@ -1051,10 +1109,8 @@
       <c r="G28" s="15" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A29" s="32" t="n">
+        <v>18</v>
       </c>
       <c r="B29" s="10" t="inlineStr"/>
       <c r="C29" s="11" t="inlineStr">
@@ -1068,10 +1124,8 @@
       <c r="G29" s="15" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A30" s="32" t="n">
+        <v>19</v>
       </c>
       <c r="B30" s="10" t="inlineStr"/>
       <c r="C30" s="11" t="inlineStr">
@@ -1084,6 +1138,8 @@
       <c r="F30" s="14" t="n"/>
       <c r="G30" s="15" t="n"/>
     </row>
+    <row r="31"/>
+    <row r="32"/>
     <row r="33">
       <c r="A33" s="16" t="inlineStr">
         <is>
@@ -1092,7 +1148,7 @@
       </c>
       <c r="D33" s="16">
         <f>COUNTIF(F5:F31,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E33" s="17" t="inlineStr">
         <is>
@@ -1103,6 +1159,7 @@
         <v>19</v>
       </c>
     </row>
+    <row r="34"/>
     <row r="35">
       <c r="A35" s="16" t="inlineStr">
         <is>
@@ -1110,13 +1167,17 @@
         </is>
       </c>
       <c r="B35" s="15" t="n"/>
+      <c r="C35" s="30" t="n"/>
+      <c r="D35" s="31" t="n"/>
       <c r="E35" s="16" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
       <c r="F35" s="15" t="n"/>
-    </row>
+      <c r="G35" s="31" t="n"/>
+    </row>
+    <row r="36"/>
     <row r="37">
       <c r="A37" s="18" t="inlineStr">
         <is>
@@ -1136,12 +1197,26 @@
     <mergeCell ref="A26:G26"/>
     <mergeCell ref="A33:C33"/>
   </mergeCells>
+  <conditionalFormatting sqref="A5:G31">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="F6 F7 F8 F9 F10 F13 F14 F15 F16 F17 F20 F21 F22 F23 F24 F27 F28 F29 F30" type="list">
-      <formula1>"✓,—"</formula1>
+    <dataValidation sqref="F6 F7 F8 F9 F10 F13 F14 F15 F16 F17 F20 F21 F22 F23 F24 F27 F28 F29 F30 F31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1150,18 +1225,18 @@
   <sheetPr>
     <tabColor rgb="00FF8C00"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="12"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1178,10 +1253,11 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -1206,7 +1282,7 @@
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Hecha</t>
+          <t>✓ Completada</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
@@ -1221,18 +1297,16 @@
           <t xml:space="preserve">  Barra Principal</t>
         </is>
       </c>
-      <c r="B5" s="20" t="n"/>
-      <c r="C5" s="20" t="n"/>
-      <c r="D5" s="20" t="n"/>
-      <c r="E5" s="20" t="n"/>
-      <c r="F5" s="20" t="n"/>
-      <c r="G5" s="20" t="n"/>
+      <c r="B5" s="30" t="n"/>
+      <c r="C5" s="30" t="n"/>
+      <c r="D5" s="30" t="n"/>
+      <c r="E5" s="30" t="n"/>
+      <c r="F5" s="30" t="n"/>
+      <c r="G5" s="31" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A6" s="32" t="n">
+        <v>1</v>
       </c>
       <c r="B6" s="10" t="inlineStr"/>
       <c r="C6" s="21" t="inlineStr">
@@ -1246,10 +1320,8 @@
       <c r="G6" s="15" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A7" s="32" t="n">
+        <v>2</v>
       </c>
       <c r="B7" s="10" t="inlineStr"/>
       <c r="C7" s="21" t="inlineStr">
@@ -1263,10 +1335,8 @@
       <c r="G7" s="15" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A8" s="32" t="n">
+        <v>3</v>
       </c>
       <c r="B8" s="10" t="inlineStr"/>
       <c r="C8" s="21" t="inlineStr">
@@ -1280,10 +1350,8 @@
       <c r="G8" s="15" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A9" s="32" t="n">
+        <v>4</v>
       </c>
       <c r="B9" s="10" t="inlineStr"/>
       <c r="C9" s="21" t="inlineStr">
@@ -1297,10 +1365,8 @@
       <c r="G9" s="15" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A10" s="32" t="n">
+        <v>5</v>
       </c>
       <c r="B10" s="10" t="inlineStr"/>
       <c r="C10" s="21" t="inlineStr">
@@ -1313,24 +1379,23 @@
       <c r="F10" s="14" t="n"/>
       <c r="G10" s="15" t="n"/>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">  Coctelería</t>
         </is>
       </c>
-      <c r="B12" s="23" t="n"/>
-      <c r="C12" s="23" t="n"/>
-      <c r="D12" s="23" t="n"/>
-      <c r="E12" s="23" t="n"/>
-      <c r="F12" s="23" t="n"/>
-      <c r="G12" s="23" t="n"/>
+      <c r="B12" s="30" t="n"/>
+      <c r="C12" s="30" t="n"/>
+      <c r="D12" s="30" t="n"/>
+      <c r="E12" s="30" t="n"/>
+      <c r="F12" s="30" t="n"/>
+      <c r="G12" s="31" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A13" s="32" t="n">
+        <v>6</v>
       </c>
       <c r="B13" s="10" t="inlineStr"/>
       <c r="C13" s="24" t="inlineStr">
@@ -1344,10 +1409,8 @@
       <c r="G13" s="15" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A14" s="32" t="n">
+        <v>7</v>
       </c>
       <c r="B14" s="10" t="inlineStr"/>
       <c r="C14" s="24" t="inlineStr">
@@ -1361,10 +1424,8 @@
       <c r="G14" s="15" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A15" s="32" t="n">
+        <v>8</v>
       </c>
       <c r="B15" s="10" t="inlineStr"/>
       <c r="C15" s="24" t="inlineStr">
@@ -1378,10 +1439,8 @@
       <c r="G15" s="15" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A16" s="32" t="n">
+        <v>9</v>
       </c>
       <c r="B16" s="10" t="inlineStr"/>
       <c r="C16" s="24" t="inlineStr">
@@ -1395,10 +1454,8 @@
       <c r="G16" s="15" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A17" s="32" t="n">
+        <v>10</v>
       </c>
       <c r="B17" s="10" t="inlineStr"/>
       <c r="C17" s="24" t="inlineStr">
@@ -1411,24 +1468,23 @@
       <c r="F17" s="14" t="n"/>
       <c r="G17" s="15" t="n"/>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  Bodega / Almacén</t>
         </is>
       </c>
-      <c r="B19" s="26" t="n"/>
-      <c r="C19" s="26" t="n"/>
-      <c r="D19" s="26" t="n"/>
-      <c r="E19" s="26" t="n"/>
-      <c r="F19" s="26" t="n"/>
-      <c r="G19" s="26" t="n"/>
+      <c r="B19" s="30" t="n"/>
+      <c r="C19" s="30" t="n"/>
+      <c r="D19" s="30" t="n"/>
+      <c r="E19" s="30" t="n"/>
+      <c r="F19" s="30" t="n"/>
+      <c r="G19" s="31" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A20" s="32" t="n">
+        <v>11</v>
       </c>
       <c r="B20" s="10" t="inlineStr"/>
       <c r="C20" s="27" t="inlineStr">
@@ -1442,10 +1498,8 @@
       <c r="G20" s="15" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A21" s="32" t="n">
+        <v>12</v>
       </c>
       <c r="B21" s="10" t="inlineStr"/>
       <c r="C21" s="27" t="inlineStr">
@@ -1459,10 +1513,8 @@
       <c r="G21" s="15" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A22" s="32" t="n">
+        <v>13</v>
       </c>
       <c r="B22" s="10" t="inlineStr"/>
       <c r="C22" s="27" t="inlineStr">
@@ -1476,10 +1528,8 @@
       <c r="G22" s="15" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A23" s="32" t="n">
+        <v>14</v>
       </c>
       <c r="B23" s="10" t="inlineStr"/>
       <c r="C23" s="27" t="inlineStr">
@@ -1492,24 +1542,23 @@
       <c r="F23" s="14" t="n"/>
       <c r="G23" s="15" t="n"/>
     </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">  Terraza</t>
         </is>
       </c>
-      <c r="B25" s="15" t="n"/>
-      <c r="C25" s="15" t="n"/>
-      <c r="D25" s="15" t="n"/>
-      <c r="E25" s="15" t="n"/>
-      <c r="F25" s="15" t="n"/>
-      <c r="G25" s="15" t="n"/>
+      <c r="B25" s="30" t="n"/>
+      <c r="C25" s="30" t="n"/>
+      <c r="D25" s="30" t="n"/>
+      <c r="E25" s="30" t="n"/>
+      <c r="F25" s="30" t="n"/>
+      <c r="G25" s="31" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A26" s="32" t="n">
+        <v>15</v>
       </c>
       <c r="B26" s="10" t="inlineStr"/>
       <c r="C26" s="29" t="inlineStr">
@@ -1523,10 +1572,8 @@
       <c r="G26" s="15" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A27" s="32" t="n">
+        <v>16</v>
       </c>
       <c r="B27" s="10" t="inlineStr"/>
       <c r="C27" s="29" t="inlineStr">
@@ -1540,10 +1587,8 @@
       <c r="G27" s="15" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A28" s="32" t="n">
+        <v>17</v>
       </c>
       <c r="B28" s="10" t="inlineStr"/>
       <c r="C28" s="29" t="inlineStr">
@@ -1557,10 +1602,8 @@
       <c r="G28" s="15" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A29" s="32" t="n">
+        <v>18</v>
       </c>
       <c r="B29" s="10" t="inlineStr"/>
       <c r="C29" s="29" t="inlineStr">
@@ -1573,6 +1616,8 @@
       <c r="F29" s="14" t="n"/>
       <c r="G29" s="15" t="n"/>
     </row>
+    <row r="30"/>
+    <row r="31"/>
     <row r="32">
       <c r="A32" s="16" t="inlineStr">
         <is>
@@ -1581,7 +1626,7 @@
       </c>
       <c r="D32" s="16">
         <f>COUNTIF(F5:F30,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E32" s="17" t="inlineStr">
         <is>
@@ -1592,6 +1637,7 @@
         <v>18</v>
       </c>
     </row>
+    <row r="33"/>
     <row r="34">
       <c r="A34" s="16" t="inlineStr">
         <is>
@@ -1599,13 +1645,17 @@
         </is>
       </c>
       <c r="B34" s="15" t="n"/>
+      <c r="C34" s="30" t="n"/>
+      <c r="D34" s="31" t="n"/>
       <c r="E34" s="16" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
       <c r="F34" s="15" t="n"/>
-    </row>
+      <c r="G34" s="31" t="n"/>
+    </row>
+    <row r="35"/>
     <row r="36">
       <c r="A36" s="18" t="inlineStr">
         <is>
@@ -1617,20 +1667,34 @@
   <mergeCells count="9">
     <mergeCell ref="A12:G12"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="A19:G19"/>
     <mergeCell ref="A32:C32"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="F34:G34"/>
     <mergeCell ref="A25:G25"/>
-    <mergeCell ref="A19:G19"/>
+    <mergeCell ref="B34:D34"/>
     <mergeCell ref="A5:G5"/>
   </mergeCells>
+  <conditionalFormatting sqref="A5:G30">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="F6 F7 F8 F9 F10 F13 F14 F15 F16 F17 F20 F21 F22 F23 F26 F27 F28 F29" type="list">
-      <formula1>"✓,—"</formula1>
+    <dataValidation sqref="F6 F7 F8 F9 F10 F13 F14 F15 F16 F17 F20 F21 F22 F23 F26 F27 F28 F29 F30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1639,18 +1703,18 @@
   <sheetPr>
     <tabColor rgb="009C27B0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="12"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1667,10 +1731,11 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -1695,7 +1760,7 @@
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Hecha</t>
+          <t>✓ Completada</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
@@ -1710,18 +1775,16 @@
           <t xml:space="preserve">  Head Bartender</t>
         </is>
       </c>
-      <c r="B5" s="8" t="n"/>
-      <c r="C5" s="8" t="n"/>
-      <c r="D5" s="8" t="n"/>
-      <c r="E5" s="8" t="n"/>
-      <c r="F5" s="8" t="n"/>
-      <c r="G5" s="8" t="n"/>
+      <c r="B5" s="30" t="n"/>
+      <c r="C5" s="30" t="n"/>
+      <c r="D5" s="30" t="n"/>
+      <c r="E5" s="30" t="n"/>
+      <c r="F5" s="30" t="n"/>
+      <c r="G5" s="31" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A6" s="32" t="n">
+        <v>1</v>
       </c>
       <c r="B6" s="10" t="inlineStr"/>
       <c r="C6" s="11" t="inlineStr">
@@ -1735,10 +1798,8 @@
       <c r="G6" s="15" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A7" s="32" t="n">
+        <v>2</v>
       </c>
       <c r="B7" s="10" t="inlineStr"/>
       <c r="C7" s="11" t="inlineStr">
@@ -1752,10 +1813,8 @@
       <c r="G7" s="15" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A8" s="32" t="n">
+        <v>3</v>
       </c>
       <c r="B8" s="10" t="inlineStr"/>
       <c r="C8" s="11" t="inlineStr">
@@ -1769,10 +1828,8 @@
       <c r="G8" s="15" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A9" s="32" t="n">
+        <v>4</v>
       </c>
       <c r="B9" s="10" t="inlineStr"/>
       <c r="C9" s="11" t="inlineStr">
@@ -1785,24 +1842,23 @@
       <c r="F9" s="14" t="n"/>
       <c r="G9" s="15" t="n"/>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Bartender</t>
         </is>
       </c>
-      <c r="B11" s="8" t="n"/>
-      <c r="C11" s="8" t="n"/>
-      <c r="D11" s="8" t="n"/>
-      <c r="E11" s="8" t="n"/>
-      <c r="F11" s="8" t="n"/>
-      <c r="G11" s="8" t="n"/>
+      <c r="B11" s="30" t="n"/>
+      <c r="C11" s="30" t="n"/>
+      <c r="D11" s="30" t="n"/>
+      <c r="E11" s="30" t="n"/>
+      <c r="F11" s="30" t="n"/>
+      <c r="G11" s="31" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A12" s="32" t="n">
+        <v>5</v>
       </c>
       <c r="B12" s="10" t="inlineStr"/>
       <c r="C12" s="11" t="inlineStr">
@@ -1816,10 +1872,8 @@
       <c r="G12" s="15" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A13" s="32" t="n">
+        <v>6</v>
       </c>
       <c r="B13" s="10" t="inlineStr"/>
       <c r="C13" s="11" t="inlineStr">
@@ -1833,10 +1887,8 @@
       <c r="G13" s="15" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A14" s="32" t="n">
+        <v>7</v>
       </c>
       <c r="B14" s="10" t="inlineStr"/>
       <c r="C14" s="11" t="inlineStr">
@@ -1850,10 +1902,8 @@
       <c r="G14" s="15" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A15" s="32" t="n">
+        <v>8</v>
       </c>
       <c r="B15" s="10" t="inlineStr"/>
       <c r="C15" s="11" t="inlineStr">
@@ -1866,24 +1916,23 @@
       <c r="F15" s="14" t="n"/>
       <c r="G15" s="15" t="n"/>
     </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Barback</t>
         </is>
       </c>
-      <c r="B17" s="8" t="n"/>
-      <c r="C17" s="8" t="n"/>
-      <c r="D17" s="8" t="n"/>
-      <c r="E17" s="8" t="n"/>
-      <c r="F17" s="8" t="n"/>
-      <c r="G17" s="8" t="n"/>
+      <c r="B17" s="30" t="n"/>
+      <c r="C17" s="30" t="n"/>
+      <c r="D17" s="30" t="n"/>
+      <c r="E17" s="30" t="n"/>
+      <c r="F17" s="30" t="n"/>
+      <c r="G17" s="31" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A18" s="32" t="n">
+        <v>9</v>
       </c>
       <c r="B18" s="10" t="inlineStr"/>
       <c r="C18" s="11" t="inlineStr">
@@ -1897,10 +1946,8 @@
       <c r="G18" s="15" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A19" s="32" t="n">
+        <v>10</v>
       </c>
       <c r="B19" s="10" t="inlineStr"/>
       <c r="C19" s="11" t="inlineStr">
@@ -1914,10 +1961,8 @@
       <c r="G19" s="15" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A20" s="32" t="n">
+        <v>11</v>
       </c>
       <c r="B20" s="10" t="inlineStr"/>
       <c r="C20" s="11" t="inlineStr">
@@ -1931,10 +1976,8 @@
       <c r="G20" s="15" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A21" s="32" t="n">
+        <v>12</v>
       </c>
       <c r="B21" s="10" t="inlineStr"/>
       <c r="C21" s="11" t="inlineStr">
@@ -1947,24 +1990,23 @@
       <c r="F21" s="14" t="n"/>
       <c r="G21" s="15" t="n"/>
     </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Camarero</t>
         </is>
       </c>
-      <c r="B23" s="8" t="n"/>
-      <c r="C23" s="8" t="n"/>
-      <c r="D23" s="8" t="n"/>
-      <c r="E23" s="8" t="n"/>
-      <c r="F23" s="8" t="n"/>
-      <c r="G23" s="8" t="n"/>
+      <c r="B23" s="30" t="n"/>
+      <c r="C23" s="30" t="n"/>
+      <c r="D23" s="30" t="n"/>
+      <c r="E23" s="30" t="n"/>
+      <c r="F23" s="30" t="n"/>
+      <c r="G23" s="31" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A24" s="32" t="n">
+        <v>13</v>
       </c>
       <c r="B24" s="10" t="inlineStr"/>
       <c r="C24" s="11" t="inlineStr">
@@ -1978,10 +2020,8 @@
       <c r="G24" s="15" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A25" s="32" t="n">
+        <v>14</v>
       </c>
       <c r="B25" s="10" t="inlineStr"/>
       <c r="C25" s="11" t="inlineStr">
@@ -1995,10 +2035,8 @@
       <c r="G25" s="15" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A26" s="32" t="n">
+        <v>15</v>
       </c>
       <c r="B26" s="10" t="inlineStr"/>
       <c r="C26" s="11" t="inlineStr">
@@ -2012,10 +2050,8 @@
       <c r="G26" s="15" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A27" s="32" t="n">
+        <v>16</v>
       </c>
       <c r="B27" s="10" t="inlineStr"/>
       <c r="C27" s="11" t="inlineStr">
@@ -2028,6 +2064,8 @@
       <c r="F27" s="14" t="n"/>
       <c r="G27" s="15" t="n"/>
     </row>
+    <row r="28"/>
+    <row r="29"/>
     <row r="30">
       <c r="A30" s="16" t="inlineStr">
         <is>
@@ -2036,7 +2074,7 @@
       </c>
       <c r="D30" s="16">
         <f>COUNTIF(F5:F28,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E30" s="17" t="inlineStr">
         <is>
@@ -2047,6 +2085,7 @@
         <v>16</v>
       </c>
     </row>
+    <row r="31"/>
     <row r="32">
       <c r="A32" s="16" t="inlineStr">
         <is>
@@ -2054,13 +2093,17 @@
         </is>
       </c>
       <c r="B32" s="15" t="n"/>
+      <c r="C32" s="30" t="n"/>
+      <c r="D32" s="31" t="n"/>
       <c r="E32" s="16" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
       <c r="F32" s="15" t="n"/>
-    </row>
+      <c r="G32" s="31" t="n"/>
+    </row>
+    <row r="33"/>
     <row r="34">
       <c r="A34" s="18" t="inlineStr">
         <is>
@@ -2080,11 +2123,25 @@
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A11:G11"/>
   </mergeCells>
+  <conditionalFormatting sqref="A5:G28">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="F6 F7 F8 F9 F12 F13 F14 F15 F18 F19 F20 F21 F24 F25 F26 F27" type="list">
-      <formula1>"✓,—"</formula1>
+    <dataValidation sqref="F6 F7 F8 F9 F12 F13 F14 F15 F18 F19 F20 F21 F24 F25 F26 F27 F28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/astro-site/public/dl/kit-tareas-bar/07-plantilla-personalizable.xlsx
+++ b/astro-site/public/dl/kit-tareas-bar/07-plantilla-personalizable.xlsx
@@ -13,9 +13,13 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Por Perfil" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Instrucciones'!$A$1:$B$38</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Por Franja Horaria'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Por Franja Horaria'!$A$1:$G$41</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Por Zona'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Por Zona'!$A$1:$G$40</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Por Perfil'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Por Perfil'!$A$1:$G$38</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -24,7 +28,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="13">
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -96,8 +100,22 @@
       <color rgb="00999999"/>
       <sz val="9"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFD700"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00333333"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <color rgb="00555555"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -138,6 +156,16 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F3E5F5"/>
         <bgColor rgb="00F3E5F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F5E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E3F2FD"/>
       </patternFill>
     </fill>
   </fills>
@@ -211,7 +239,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -268,6 +296,69 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -645,71 +736,185 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="80" customWidth="1" min="2" max="2"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1"/>
-    <row r="2">
-      <c r="B2" s="1" t="inlineStr">
+    <row r="2" ht="26" customHeight="1">
+      <c r="B2" s="33" t="inlineStr">
         <is>
           <t>07 — Plantilla Personalizable · Bar / Cocktails</t>
         </is>
       </c>
     </row>
     <row r="3"/>
-    <row r="4">
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Plantillas en blanco para crear tus propias listas de tareas.</t>
+    <row r="4" ht="18" customHeight="1">
+      <c r="B4" s="34" t="inlineStr">
+        <is>
+          <t>Qué resuelve</t>
         </is>
       </c>
     </row>
     <row r="5"/>
-    <row r="6">
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Cómo usar:</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>▸ Copia la pestaña que más se ajuste</t>
+    <row r="6" ht="32" customHeight="1">
+      <c r="B6" s="35" t="inlineStr">
+        <is>
+          <t>▸ Tres plantillas maestras ya estructuradas —por franja horaria, por área y por perfil— con las secciones puestas y la zona o el responsable precargados: tú sólo escribes tus tareas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="32" customHeight="1">
+      <c r="B7" s="35" t="inlineStr">
+        <is>
+          <t>▸ Escribe en las celdas VERDES de la columna «Tarea», bajo la sección que corresponda. El contador arranca en 0 y sube a medida que escribes: cuenta lo que hay, no un número fijo.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>▸ Rellena con las tareas específicas de tu bar</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>▸ Imprime en A4 y distribuye al equipo</t>
+      <c r="B8" s="3" t="n"/>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="B9" s="34" t="inlineStr">
+        <is>
+          <t>Cómo cuenta el contador</t>
         </is>
       </c>
     </row>
     <row r="10"/>
-    <row r="11">
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>Marca con ✓ en la columna «✓ Completada» (desplegable): es la que cuenta el total de tareas completadas.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas-bar · info@aichef.pro</t>
+    <row r="11" ht="32" customHeight="1">
+      <c r="B11" s="35" t="inlineStr">
+        <is>
+          <t>▸ Marca con ✓ en la columna «✓ Completada» (desplegable): es la que cuenta el total de tareas completadas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="32" customHeight="1">
+      <c r="B12" s="35" t="inlineStr">
+        <is>
+          <t>▸ «N/A» = no aplica en tu local: esa tarea SALE del total (no la borres, márcala N/A). «—» = no hecha: sigue contando como pendiente y baja el porcentaje, que es de lo que se trata.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="32" customHeight="1">
+      <c r="B13" s="35" t="inlineStr">
+        <is>
+          <t>▸ El denominador cuenta las tareas escritas en la columna «Tarea», no un número fijo: si añades o borras tareas, el total se ajusta solo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="B15" s="34" t="inlineStr">
+        <is>
+          <t>Filas libres</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="32" customHeight="1">
+      <c r="B17" s="35" t="inlineStr">
+        <is>
+          <t>▸ Al final de cada tabla hay 5 filas verdes libres DENTRO del rango que cuenta el contador: escribe ahí tus tareas propias.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="32" customHeight="1">
+      <c r="B18" s="35" t="inlineStr">
+        <is>
+          <t>▸ Si necesitas más, inserta filas DENTRO de la tabla (clic derecho → Insertar), nunca por debajo de la última: lo que se escriba fuera del rango no lo cuenta nadie.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="B20" s="34" t="inlineStr">
+        <is>
+          <t>Protección de la hoja</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="32" customHeight="1">
+      <c r="B22" s="35" t="inlineStr">
+        <is>
+          <t>▸ Las hojas con fórmulas van protegidas SIN contraseña: las celdas de entrada (las verdes) están desbloqueadas y los cálculos no se pisan por accidente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="32" customHeight="1">
+      <c r="B23" s="35" t="inlineStr">
+        <is>
+          <t>▸ Puedes insertar y borrar filas con la protección puesta. Para cambiar la estructura: Revisar → Desproteger hoja.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="B25" s="34" t="inlineStr">
+        <is>
+          <t>Se conecta con</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="16" customHeight="1">
+      <c r="B27" s="35" t="inlineStr">
+        <is>
+          <t>▸ 08-apertura-cierre-negocio.xlsx — checklist del LOCAL completo: es el MARCO del día.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="16" customHeight="1">
+      <c r="B28" s="35" t="inlineStr">
+        <is>
+          <t>▸ 01-apertura-cierre.xlsx — el mismo día con el DETALLE por área (barra).</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="16" customHeight="1">
+      <c r="B29" s="35" t="inlineStr">
+        <is>
+          <t>▸ 09-apertura-cierre-caja.xlsx — la CAJA: fondo, recuento por denominaciones, Z del TPV y descuadre.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="48" customHeight="1">
+      <c r="B30" s="35" t="inlineStr">
+        <is>
+          <t>▸ Orden de uso: local → áreas → caja. Cada fichero cubre un nivel: el de negocio marca el HITO (encender, abrir, cerrar), el de áreas detalla CÓMO se hace en cada zona y el de caja lleva el DINERO. Si una tarea aparece en dos, es a propósito: una es el hito y la otra el detalle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="32" customHeight="1">
+      <c r="B31" s="35" t="inlineStr">
+        <is>
+          <t>▸ Estás en 07-plantilla-personalizable.xlsx: aquí construyes TUS listas cuando ninguna de las otras encaja. Copia la estructura de la que más se parezca.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="B33" s="34" t="inlineStr">
+        <is>
+          <t>— Kit de Tareas Recurrentes · Bar / Cocktails · AI Chef Pro · aichef.pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="35" customHeight="1">
+      <c r="B35" s="34" t="inlineStr">
+        <is>
+          <t>Diseñado por John Guerrero — chef y consultor gastronómico desde 2010, en cocina desde los 17 años · johnguerrero.es</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="18" customHeight="1">
+      <c r="B36" s="34" t="inlineStr">
+        <is>
+          <t>Contacto: info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="18" customHeight="1">
+      <c r="B38" s="34" t="inlineStr">
+        <is>
+          <t>Versión 2.0 · agosto 2026 · aichef.pro/kit-tareas-bar · info@aichef.pro</t>
         </is>
       </c>
     </row>
@@ -734,7 +939,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -799,411 +1004,421 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Apertura (15:00 - 18:00)</t>
-        </is>
-      </c>
-      <c r="B5" s="30" t="n"/>
-      <c r="C5" s="30" t="n"/>
-      <c r="D5" s="30" t="n"/>
-      <c r="E5" s="30" t="n"/>
-      <c r="F5" s="30" t="n"/>
-      <c r="G5" s="31" t="n"/>
+      <c r="A5" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Apertura (15:00 - 18:00) — escribe aquí abajo tus tareas</t>
+        </is>
+      </c>
+      <c r="B5" s="37" t="n"/>
+      <c r="C5" s="37" t="n"/>
+      <c r="D5" s="37" t="n"/>
+      <c r="E5" s="37" t="n"/>
+      <c r="F5" s="37" t="n"/>
+      <c r="G5" s="38" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="32" t="n">
+      <c r="A6" s="39" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="10" t="inlineStr"/>
-      <c r="C6" s="11" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="D6" s="12" t="inlineStr"/>
-      <c r="E6" s="13" t="inlineStr"/>
-      <c r="F6" s="14" t="n"/>
-      <c r="G6" s="15" t="n"/>
+      <c r="B6" s="40" t="inlineStr"/>
+      <c r="C6" s="41" t="n"/>
+      <c r="D6" s="42" t="inlineStr">
+        <is>
+          <t>(Responsable)</t>
+        </is>
+      </c>
+      <c r="E6" s="42" t="inlineStr"/>
+      <c r="F6" s="43" t="n"/>
+      <c r="G6" s="44" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="32" t="n">
+      <c r="A7" s="39" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="10" t="inlineStr"/>
-      <c r="C7" s="11" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="D7" s="12" t="inlineStr"/>
-      <c r="E7" s="13" t="inlineStr"/>
-      <c r="F7" s="14" t="n"/>
-      <c r="G7" s="15" t="n"/>
+      <c r="B7" s="40" t="inlineStr"/>
+      <c r="C7" s="41" t="n"/>
+      <c r="D7" s="42" t="inlineStr"/>
+      <c r="E7" s="42" t="inlineStr"/>
+      <c r="F7" s="43" t="n"/>
+      <c r="G7" s="44" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="32" t="n">
+      <c r="A8" s="39" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="10" t="inlineStr"/>
-      <c r="C8" s="11" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="D8" s="12" t="inlineStr"/>
-      <c r="E8" s="13" t="inlineStr"/>
-      <c r="F8" s="14" t="n"/>
-      <c r="G8" s="15" t="n"/>
+      <c r="B8" s="40" t="inlineStr"/>
+      <c r="C8" s="41" t="n"/>
+      <c r="D8" s="42" t="inlineStr"/>
+      <c r="E8" s="42" t="inlineStr"/>
+      <c r="F8" s="43" t="n"/>
+      <c r="G8" s="44" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="32" t="n">
+      <c r="A9" s="39" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="10" t="inlineStr"/>
-      <c r="C9" s="11" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="D9" s="12" t="inlineStr"/>
-      <c r="E9" s="13" t="inlineStr"/>
-      <c r="F9" s="14" t="n"/>
-      <c r="G9" s="15" t="n"/>
+      <c r="B9" s="40" t="inlineStr"/>
+      <c r="C9" s="41" t="n"/>
+      <c r="D9" s="42" t="inlineStr"/>
+      <c r="E9" s="42" t="inlineStr"/>
+      <c r="F9" s="43" t="n"/>
+      <c r="G9" s="44" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="32" t="n">
+      <c r="A10" s="39" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="10" t="inlineStr"/>
-      <c r="C10" s="11" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="D10" s="12" t="inlineStr"/>
-      <c r="E10" s="13" t="inlineStr"/>
-      <c r="F10" s="14" t="n"/>
-      <c r="G10" s="15" t="n"/>
-    </row>
-    <row r="11"/>
+      <c r="B10" s="40" t="inlineStr"/>
+      <c r="C10" s="41" t="n"/>
+      <c r="D10" s="42" t="inlineStr"/>
+      <c r="E10" s="42" t="inlineStr"/>
+      <c r="F10" s="43" t="n"/>
+      <c r="G10" s="44" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="45" t="n"/>
+      <c r="B11" s="45" t="n"/>
+      <c r="C11" s="45" t="n"/>
+      <c r="D11" s="45" t="n"/>
+      <c r="E11" s="45" t="n"/>
+      <c r="F11" s="45" t="n"/>
+      <c r="G11" s="45" t="n"/>
+    </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Servicio Tarde (18:00 - 22:00)</t>
-        </is>
-      </c>
-      <c r="B12" s="30" t="n"/>
-      <c r="C12" s="30" t="n"/>
-      <c r="D12" s="30" t="n"/>
-      <c r="E12" s="30" t="n"/>
-      <c r="F12" s="30" t="n"/>
-      <c r="G12" s="31" t="n"/>
+      <c r="A12" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Servicio Tarde (18:00 - 22:00) — escribe aquí abajo tus tareas</t>
+        </is>
+      </c>
+      <c r="B12" s="37" t="n"/>
+      <c r="C12" s="37" t="n"/>
+      <c r="D12" s="37" t="n"/>
+      <c r="E12" s="37" t="n"/>
+      <c r="F12" s="37" t="n"/>
+      <c r="G12" s="38" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="32" t="n">
+      <c r="A13" s="39" t="n">
         <v>6</v>
       </c>
-      <c r="B13" s="10" t="inlineStr"/>
-      <c r="C13" s="11" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="D13" s="12" t="inlineStr"/>
-      <c r="E13" s="13" t="inlineStr"/>
-      <c r="F13" s="14" t="n"/>
-      <c r="G13" s="15" t="n"/>
+      <c r="B13" s="40" t="inlineStr"/>
+      <c r="C13" s="41" t="n"/>
+      <c r="D13" s="42" t="inlineStr">
+        <is>
+          <t>(Responsable)</t>
+        </is>
+      </c>
+      <c r="E13" s="42" t="inlineStr"/>
+      <c r="F13" s="43" t="n"/>
+      <c r="G13" s="44" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="32" t="n">
+      <c r="A14" s="39" t="n">
         <v>7</v>
       </c>
-      <c r="B14" s="10" t="inlineStr"/>
-      <c r="C14" s="11" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="D14" s="12" t="inlineStr"/>
-      <c r="E14" s="13" t="inlineStr"/>
-      <c r="F14" s="14" t="n"/>
-      <c r="G14" s="15" t="n"/>
+      <c r="B14" s="40" t="inlineStr"/>
+      <c r="C14" s="41" t="n"/>
+      <c r="D14" s="42" t="inlineStr"/>
+      <c r="E14" s="42" t="inlineStr"/>
+      <c r="F14" s="43" t="n"/>
+      <c r="G14" s="44" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="32" t="n">
+      <c r="A15" s="39" t="n">
         <v>8</v>
       </c>
-      <c r="B15" s="10" t="inlineStr"/>
-      <c r="C15" s="11" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="D15" s="12" t="inlineStr"/>
-      <c r="E15" s="13" t="inlineStr"/>
-      <c r="F15" s="14" t="n"/>
-      <c r="G15" s="15" t="n"/>
+      <c r="B15" s="40" t="inlineStr"/>
+      <c r="C15" s="41" t="n"/>
+      <c r="D15" s="42" t="inlineStr"/>
+      <c r="E15" s="42" t="inlineStr"/>
+      <c r="F15" s="43" t="n"/>
+      <c r="G15" s="44" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="32" t="n">
+      <c r="A16" s="39" t="n">
         <v>9</v>
       </c>
-      <c r="B16" s="10" t="inlineStr"/>
-      <c r="C16" s="11" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="D16" s="12" t="inlineStr"/>
-      <c r="E16" s="13" t="inlineStr"/>
-      <c r="F16" s="14" t="n"/>
-      <c r="G16" s="15" t="n"/>
+      <c r="B16" s="40" t="inlineStr"/>
+      <c r="C16" s="41" t="n"/>
+      <c r="D16" s="42" t="inlineStr"/>
+      <c r="E16" s="42" t="inlineStr"/>
+      <c r="F16" s="43" t="n"/>
+      <c r="G16" s="44" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="32" t="n">
+      <c r="A17" s="39" t="n">
         <v>10</v>
       </c>
-      <c r="B17" s="10" t="inlineStr"/>
-      <c r="C17" s="11" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="D17" s="12" t="inlineStr"/>
-      <c r="E17" s="13" t="inlineStr"/>
-      <c r="F17" s="14" t="n"/>
-      <c r="G17" s="15" t="n"/>
-    </row>
-    <row r="18"/>
+      <c r="B17" s="40" t="inlineStr"/>
+      <c r="C17" s="41" t="n"/>
+      <c r="D17" s="42" t="inlineStr"/>
+      <c r="E17" s="42" t="inlineStr"/>
+      <c r="F17" s="43" t="n"/>
+      <c r="G17" s="44" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="45" t="n"/>
+      <c r="B18" s="45" t="n"/>
+      <c r="C18" s="45" t="n"/>
+      <c r="D18" s="45" t="n"/>
+      <c r="E18" s="45" t="n"/>
+      <c r="F18" s="45" t="n"/>
+      <c r="G18" s="45" t="n"/>
+    </row>
     <row r="19">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Servicio Noche (22:00 - 02:00)</t>
-        </is>
-      </c>
-      <c r="B19" s="30" t="n"/>
-      <c r="C19" s="30" t="n"/>
-      <c r="D19" s="30" t="n"/>
-      <c r="E19" s="30" t="n"/>
-      <c r="F19" s="30" t="n"/>
-      <c r="G19" s="31" t="n"/>
+      <c r="A19" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Servicio Noche (22:00 - 02:00) — escribe aquí abajo tus tareas</t>
+        </is>
+      </c>
+      <c r="B19" s="37" t="n"/>
+      <c r="C19" s="37" t="n"/>
+      <c r="D19" s="37" t="n"/>
+      <c r="E19" s="37" t="n"/>
+      <c r="F19" s="37" t="n"/>
+      <c r="G19" s="38" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="32" t="n">
+      <c r="A20" s="39" t="n">
         <v>11</v>
       </c>
-      <c r="B20" s="10" t="inlineStr"/>
-      <c r="C20" s="11" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="D20" s="12" t="inlineStr"/>
-      <c r="E20" s="13" t="inlineStr"/>
-      <c r="F20" s="14" t="n"/>
-      <c r="G20" s="15" t="n"/>
+      <c r="B20" s="40" t="inlineStr"/>
+      <c r="C20" s="41" t="n"/>
+      <c r="D20" s="42" t="inlineStr">
+        <is>
+          <t>(Responsable)</t>
+        </is>
+      </c>
+      <c r="E20" s="42" t="inlineStr"/>
+      <c r="F20" s="43" t="n"/>
+      <c r="G20" s="44" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="32" t="n">
+      <c r="A21" s="39" t="n">
         <v>12</v>
       </c>
-      <c r="B21" s="10" t="inlineStr"/>
-      <c r="C21" s="11" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="D21" s="12" t="inlineStr"/>
-      <c r="E21" s="13" t="inlineStr"/>
-      <c r="F21" s="14" t="n"/>
-      <c r="G21" s="15" t="n"/>
+      <c r="B21" s="40" t="inlineStr"/>
+      <c r="C21" s="41" t="n"/>
+      <c r="D21" s="42" t="inlineStr"/>
+      <c r="E21" s="42" t="inlineStr"/>
+      <c r="F21" s="43" t="n"/>
+      <c r="G21" s="44" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="32" t="n">
+      <c r="A22" s="39" t="n">
         <v>13</v>
       </c>
-      <c r="B22" s="10" t="inlineStr"/>
-      <c r="C22" s="11" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="D22" s="12" t="inlineStr"/>
-      <c r="E22" s="13" t="inlineStr"/>
-      <c r="F22" s="14" t="n"/>
-      <c r="G22" s="15" t="n"/>
+      <c r="B22" s="40" t="inlineStr"/>
+      <c r="C22" s="41" t="n"/>
+      <c r="D22" s="42" t="inlineStr"/>
+      <c r="E22" s="42" t="inlineStr"/>
+      <c r="F22" s="43" t="n"/>
+      <c r="G22" s="44" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="32" t="n">
+      <c r="A23" s="39" t="n">
         <v>14</v>
       </c>
-      <c r="B23" s="10" t="inlineStr"/>
-      <c r="C23" s="11" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="D23" s="12" t="inlineStr"/>
-      <c r="E23" s="13" t="inlineStr"/>
-      <c r="F23" s="14" t="n"/>
-      <c r="G23" s="15" t="n"/>
+      <c r="B23" s="40" t="inlineStr"/>
+      <c r="C23" s="41" t="n"/>
+      <c r="D23" s="42" t="inlineStr"/>
+      <c r="E23" s="42" t="inlineStr"/>
+      <c r="F23" s="43" t="n"/>
+      <c r="G23" s="44" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="32" t="n">
+      <c r="A24" s="39" t="n">
         <v>15</v>
       </c>
-      <c r="B24" s="10" t="inlineStr"/>
-      <c r="C24" s="11" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="D24" s="12" t="inlineStr"/>
-      <c r="E24" s="13" t="inlineStr"/>
-      <c r="F24" s="14" t="n"/>
-      <c r="G24" s="15" t="n"/>
-    </row>
-    <row r="25"/>
+      <c r="B24" s="40" t="inlineStr"/>
+      <c r="C24" s="41" t="n"/>
+      <c r="D24" s="42" t="inlineStr"/>
+      <c r="E24" s="42" t="inlineStr"/>
+      <c r="F24" s="43" t="n"/>
+      <c r="G24" s="44" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="45" t="n"/>
+      <c r="B25" s="45" t="n"/>
+      <c r="C25" s="45" t="n"/>
+      <c r="D25" s="45" t="n"/>
+      <c r="E25" s="45" t="n"/>
+      <c r="F25" s="45" t="n"/>
+      <c r="G25" s="45" t="n"/>
+    </row>
     <row r="26">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Cierre (02:00 - 03:00)</t>
-        </is>
-      </c>
-      <c r="B26" s="30" t="n"/>
-      <c r="C26" s="30" t="n"/>
-      <c r="D26" s="30" t="n"/>
-      <c r="E26" s="30" t="n"/>
-      <c r="F26" s="30" t="n"/>
-      <c r="G26" s="31" t="n"/>
+      <c r="A26" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Cierre (02:00 - 03:00) — escribe aquí abajo tus tareas</t>
+        </is>
+      </c>
+      <c r="B26" s="37" t="n"/>
+      <c r="C26" s="37" t="n"/>
+      <c r="D26" s="37" t="n"/>
+      <c r="E26" s="37" t="n"/>
+      <c r="F26" s="37" t="n"/>
+      <c r="G26" s="38" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="32" t="n">
+      <c r="A27" s="39" t="n">
         <v>16</v>
       </c>
-      <c r="B27" s="10" t="inlineStr"/>
-      <c r="C27" s="11" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="D27" s="12" t="inlineStr"/>
-      <c r="E27" s="13" t="inlineStr"/>
-      <c r="F27" s="14" t="n"/>
-      <c r="G27" s="15" t="n"/>
+      <c r="B27" s="40" t="inlineStr"/>
+      <c r="C27" s="41" t="n"/>
+      <c r="D27" s="42" t="inlineStr">
+        <is>
+          <t>(Responsable)</t>
+        </is>
+      </c>
+      <c r="E27" s="42" t="inlineStr"/>
+      <c r="F27" s="43" t="n"/>
+      <c r="G27" s="44" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="32" t="n">
+      <c r="A28" s="39" t="n">
         <v>17</v>
       </c>
-      <c r="B28" s="10" t="inlineStr"/>
-      <c r="C28" s="11" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="D28" s="12" t="inlineStr"/>
-      <c r="E28" s="13" t="inlineStr"/>
-      <c r="F28" s="14" t="n"/>
-      <c r="G28" s="15" t="n"/>
+      <c r="B28" s="40" t="inlineStr"/>
+      <c r="C28" s="41" t="n"/>
+      <c r="D28" s="42" t="inlineStr"/>
+      <c r="E28" s="42" t="inlineStr"/>
+      <c r="F28" s="43" t="n"/>
+      <c r="G28" s="44" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="32" t="n">
+      <c r="A29" s="39" t="n">
         <v>18</v>
       </c>
-      <c r="B29" s="10" t="inlineStr"/>
-      <c r="C29" s="11" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="D29" s="12" t="inlineStr"/>
-      <c r="E29" s="13" t="inlineStr"/>
-      <c r="F29" s="14" t="n"/>
-      <c r="G29" s="15" t="n"/>
+      <c r="B29" s="40" t="inlineStr"/>
+      <c r="C29" s="41" t="n"/>
+      <c r="D29" s="42" t="inlineStr"/>
+      <c r="E29" s="42" t="inlineStr"/>
+      <c r="F29" s="43" t="n"/>
+      <c r="G29" s="44" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="32" t="n">
+      <c r="A30" s="39" t="n">
         <v>19</v>
       </c>
-      <c r="B30" s="10" t="inlineStr"/>
-      <c r="C30" s="11" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="D30" s="12" t="inlineStr"/>
-      <c r="E30" s="13" t="inlineStr"/>
-      <c r="F30" s="14" t="n"/>
-      <c r="G30" s="15" t="n"/>
-    </row>
-    <row r="31"/>
-    <row r="32"/>
+      <c r="B30" s="40" t="inlineStr"/>
+      <c r="C30" s="41" t="n"/>
+      <c r="D30" s="42" t="inlineStr"/>
+      <c r="E30" s="42" t="inlineStr"/>
+      <c r="F30" s="43" t="n"/>
+      <c r="G30" s="44" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="46" t="n"/>
+      <c r="B31" s="40" t="n"/>
+      <c r="C31" s="41" t="n"/>
+      <c r="D31" s="42" t="n"/>
+      <c r="E31" s="42" t="n"/>
+      <c r="F31" s="43" t="n"/>
+      <c r="G31" s="44" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="46" t="n"/>
+      <c r="B32" s="40" t="n"/>
+      <c r="C32" s="41" t="n"/>
+      <c r="D32" s="42" t="n"/>
+      <c r="E32" s="42" t="n"/>
+      <c r="F32" s="43" t="n"/>
+      <c r="G32" s="44" t="n"/>
+    </row>
     <row r="33">
-      <c r="A33" s="16" t="inlineStr">
-        <is>
-          <t>Tareas completadas:</t>
-        </is>
-      </c>
-      <c r="D33" s="16">
-        <f>COUNTIF(F5:F31,"✓")</f>
-        <v>0.0</v>
-      </c>
-      <c r="E33" s="17" t="inlineStr">
-        <is>
-          <t>de</t>
-        </is>
-      </c>
-      <c r="F33" s="16" t="n">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="34"/>
+      <c r="A33" s="46" t="n"/>
+      <c r="B33" s="40" t="n"/>
+      <c r="C33" s="41" t="n"/>
+      <c r="D33" s="42" t="n"/>
+      <c r="E33" s="42" t="n"/>
+      <c r="F33" s="43" t="n"/>
+      <c r="G33" s="44" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="46" t="n"/>
+      <c r="B34" s="40" t="n"/>
+      <c r="C34" s="41" t="n"/>
+      <c r="D34" s="42" t="n"/>
+      <c r="E34" s="42" t="n"/>
+      <c r="F34" s="43" t="n"/>
+      <c r="G34" s="44" t="n"/>
+    </row>
     <row r="35">
-      <c r="A35" s="16" t="inlineStr">
-        <is>
-          <t>Verificado por:</t>
-        </is>
-      </c>
-      <c r="B35" s="15" t="n"/>
-      <c r="C35" s="30" t="n"/>
-      <c r="D35" s="31" t="n"/>
-      <c r="E35" s="16" t="inlineStr">
-        <is>
-          <t>Firma:</t>
-        </is>
-      </c>
-      <c r="F35" s="15" t="n"/>
-      <c r="G35" s="31" t="n"/>
+      <c r="A35" s="46" t="n"/>
+      <c r="B35" s="40" t="n"/>
+      <c r="C35" s="41" t="n"/>
+      <c r="D35" s="42" t="n"/>
+      <c r="E35" s="42" t="n"/>
+      <c r="F35" s="43" t="n"/>
+      <c r="G35" s="44" t="n"/>
     </row>
     <row r="36"/>
     <row r="37">
-      <c r="A37" s="18" t="inlineStr">
+      <c r="A37" s="16" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="D37" s="16">
+        <f>COUNTIFS(B5:B35,"?*",F5:F35,"✓")</f>
+        <v>0.0</v>
+      </c>
+      <c r="E37" s="17" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="F37" s="16">
+        <f>COUNTIF(B5:B35,"?*")-COUNTIF(F5:F35,"N/A")</f>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="38"/>
+    <row r="39">
+      <c r="A39" s="16" t="inlineStr">
+        <is>
+          <t>Verificado por:</t>
+        </is>
+      </c>
+      <c r="B39" s="47" t="n"/>
+      <c r="C39" s="30" t="n"/>
+      <c r="D39" s="31" t="n"/>
+      <c r="E39" s="16" t="inlineStr">
+        <is>
+          <t>Firma:</t>
+        </is>
+      </c>
+      <c r="F39" s="47" t="n"/>
+      <c r="G39" s="31" t="n"/>
+    </row>
+    <row r="40"/>
+    <row r="41">
+      <c r="A41" s="18" t="inlineStr">
         <is>
           <t>— Kit de Tareas Recurrentes · Bar / Cocktails · AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
   <mergeCells count="9">
-    <mergeCell ref="F35:G35"/>
     <mergeCell ref="A12:G12"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="B35:D35"/>
     <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A37:C37"/>
+    <mergeCell ref="F39:G39"/>
     <mergeCell ref="A19:G19"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A26:G26"/>
-    <mergeCell ref="A33:C33"/>
+    <mergeCell ref="B39:D39"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:G31">
+  <conditionalFormatting sqref="A5:G35">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$F5="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F10 F13 F14 F15 F16 F17 F20 F21 F22 F23 F24 F27 F28 F29 F30 F31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F13 F14 F15 F16 F17 F20 F21 F22 F23 F24 F27 F28 F29 F30 F31 F32 F33 F34 F35" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." type="list" errorStyle="stop">
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1227,7 +1442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G36"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1249,7 +1464,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Fecha: ___/___/______    Turno: ☐ Mañana  ☐ Tarde  ☐ Noche    Responsable turno: _________________________</t>
+          <t>Fecha: ___/___/______    Responsable: _________________________</t>
         </is>
       </c>
     </row>
@@ -1292,396 +1507,482 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Barra Principal</t>
-        </is>
-      </c>
-      <c r="B5" s="30" t="n"/>
-      <c r="C5" s="30" t="n"/>
-      <c r="D5" s="30" t="n"/>
-      <c r="E5" s="30" t="n"/>
-      <c r="F5" s="30" t="n"/>
-      <c r="G5" s="31" t="n"/>
+      <c r="A5" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Barra Principal — escribe aquí abajo tus tareas</t>
+        </is>
+      </c>
+      <c r="B5" s="37" t="n"/>
+      <c r="C5" s="37" t="n"/>
+      <c r="D5" s="37" t="n"/>
+      <c r="E5" s="37" t="n"/>
+      <c r="F5" s="37" t="n"/>
+      <c r="G5" s="38" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="32" t="n">
+      <c r="A6" s="39" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="10" t="inlineStr"/>
-      <c r="C6" s="21" t="inlineStr">
+      <c r="B6" s="40" t="inlineStr"/>
+      <c r="C6" s="41" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D6" s="12" t="inlineStr"/>
-      <c r="E6" s="13" t="inlineStr"/>
-      <c r="F6" s="14" t="n"/>
-      <c r="G6" s="15" t="n"/>
+      <c r="D6" s="42" t="inlineStr">
+        <is>
+          <t>(Responsable)</t>
+        </is>
+      </c>
+      <c r="E6" s="42" t="inlineStr"/>
+      <c r="F6" s="43" t="n"/>
+      <c r="G6" s="44" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="32" t="n">
+      <c r="A7" s="39" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="10" t="inlineStr"/>
-      <c r="C7" s="21" t="inlineStr">
+      <c r="B7" s="40" t="inlineStr"/>
+      <c r="C7" s="41" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D7" s="12" t="inlineStr"/>
-      <c r="E7" s="13" t="inlineStr"/>
-      <c r="F7" s="14" t="n"/>
-      <c r="G7" s="15" t="n"/>
+      <c r="D7" s="42" t="inlineStr"/>
+      <c r="E7" s="42" t="inlineStr"/>
+      <c r="F7" s="43" t="n"/>
+      <c r="G7" s="44" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="32" t="n">
+      <c r="A8" s="39" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="10" t="inlineStr"/>
-      <c r="C8" s="21" t="inlineStr">
+      <c r="B8" s="40" t="inlineStr"/>
+      <c r="C8" s="41" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D8" s="12" t="inlineStr"/>
-      <c r="E8" s="13" t="inlineStr"/>
-      <c r="F8" s="14" t="n"/>
-      <c r="G8" s="15" t="n"/>
+      <c r="D8" s="42" t="inlineStr"/>
+      <c r="E8" s="42" t="inlineStr"/>
+      <c r="F8" s="43" t="n"/>
+      <c r="G8" s="44" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="32" t="n">
+      <c r="A9" s="39" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="10" t="inlineStr"/>
-      <c r="C9" s="21" t="inlineStr">
+      <c r="B9" s="40" t="inlineStr"/>
+      <c r="C9" s="41" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D9" s="12" t="inlineStr"/>
-      <c r="E9" s="13" t="inlineStr"/>
-      <c r="F9" s="14" t="n"/>
-      <c r="G9" s="15" t="n"/>
+      <c r="D9" s="42" t="inlineStr"/>
+      <c r="E9" s="42" t="inlineStr"/>
+      <c r="F9" s="43" t="n"/>
+      <c r="G9" s="44" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="32" t="n">
+      <c r="A10" s="39" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="10" t="inlineStr"/>
-      <c r="C10" s="21" t="inlineStr">
+      <c r="B10" s="40" t="inlineStr"/>
+      <c r="C10" s="41" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D10" s="12" t="inlineStr"/>
-      <c r="E10" s="13" t="inlineStr"/>
-      <c r="F10" s="14" t="n"/>
-      <c r="G10" s="15" t="n"/>
-    </row>
-    <row r="11"/>
+      <c r="D10" s="42" t="inlineStr"/>
+      <c r="E10" s="42" t="inlineStr"/>
+      <c r="F10" s="43" t="n"/>
+      <c r="G10" s="44" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="45" t="n"/>
+      <c r="B11" s="45" t="n"/>
+      <c r="C11" s="45" t="n"/>
+      <c r="D11" s="45" t="n"/>
+      <c r="E11" s="45" t="n"/>
+      <c r="F11" s="45" t="n"/>
+      <c r="G11" s="45" t="n"/>
+    </row>
     <row r="12">
-      <c r="A12" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Coctelería</t>
-        </is>
-      </c>
-      <c r="B12" s="30" t="n"/>
-      <c r="C12" s="30" t="n"/>
-      <c r="D12" s="30" t="n"/>
-      <c r="E12" s="30" t="n"/>
-      <c r="F12" s="30" t="n"/>
-      <c r="G12" s="31" t="n"/>
+      <c r="A12" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Coctelería — escribe aquí abajo tus tareas</t>
+        </is>
+      </c>
+      <c r="B12" s="37" t="n"/>
+      <c r="C12" s="37" t="n"/>
+      <c r="D12" s="37" t="n"/>
+      <c r="E12" s="37" t="n"/>
+      <c r="F12" s="37" t="n"/>
+      <c r="G12" s="38" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="32" t="n">
+      <c r="A13" s="39" t="n">
         <v>6</v>
       </c>
-      <c r="B13" s="10" t="inlineStr"/>
-      <c r="C13" s="24" t="inlineStr">
+      <c r="B13" s="40" t="inlineStr"/>
+      <c r="C13" s="41" t="inlineStr">
         <is>
           <t>Coctelería</t>
         </is>
       </c>
-      <c r="D13" s="12" t="inlineStr"/>
-      <c r="E13" s="13" t="inlineStr"/>
-      <c r="F13" s="14" t="n"/>
-      <c r="G13" s="15" t="n"/>
+      <c r="D13" s="42" t="inlineStr">
+        <is>
+          <t>(Responsable)</t>
+        </is>
+      </c>
+      <c r="E13" s="42" t="inlineStr"/>
+      <c r="F13" s="43" t="n"/>
+      <c r="G13" s="44" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="32" t="n">
+      <c r="A14" s="39" t="n">
         <v>7</v>
       </c>
-      <c r="B14" s="10" t="inlineStr"/>
-      <c r="C14" s="24" t="inlineStr">
+      <c r="B14" s="40" t="inlineStr"/>
+      <c r="C14" s="41" t="inlineStr">
         <is>
           <t>Coctelería</t>
         </is>
       </c>
-      <c r="D14" s="12" t="inlineStr"/>
-      <c r="E14" s="13" t="inlineStr"/>
-      <c r="F14" s="14" t="n"/>
-      <c r="G14" s="15" t="n"/>
+      <c r="D14" s="42" t="inlineStr"/>
+      <c r="E14" s="42" t="inlineStr"/>
+      <c r="F14" s="43" t="n"/>
+      <c r="G14" s="44" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="32" t="n">
+      <c r="A15" s="39" t="n">
         <v>8</v>
       </c>
-      <c r="B15" s="10" t="inlineStr"/>
-      <c r="C15" s="24" t="inlineStr">
+      <c r="B15" s="40" t="inlineStr"/>
+      <c r="C15" s="41" t="inlineStr">
         <is>
           <t>Coctelería</t>
         </is>
       </c>
-      <c r="D15" s="12" t="inlineStr"/>
-      <c r="E15" s="13" t="inlineStr"/>
-      <c r="F15" s="14" t="n"/>
-      <c r="G15" s="15" t="n"/>
+      <c r="D15" s="42" t="inlineStr"/>
+      <c r="E15" s="42" t="inlineStr"/>
+      <c r="F15" s="43" t="n"/>
+      <c r="G15" s="44" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="32" t="n">
+      <c r="A16" s="39" t="n">
         <v>9</v>
       </c>
-      <c r="B16" s="10" t="inlineStr"/>
-      <c r="C16" s="24" t="inlineStr">
+      <c r="B16" s="40" t="inlineStr"/>
+      <c r="C16" s="41" t="inlineStr">
         <is>
           <t>Coctelería</t>
         </is>
       </c>
-      <c r="D16" s="12" t="inlineStr"/>
-      <c r="E16" s="13" t="inlineStr"/>
-      <c r="F16" s="14" t="n"/>
-      <c r="G16" s="15" t="n"/>
+      <c r="D16" s="42" t="inlineStr"/>
+      <c r="E16" s="42" t="inlineStr"/>
+      <c r="F16" s="43" t="n"/>
+      <c r="G16" s="44" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="32" t="n">
+      <c r="A17" s="39" t="n">
         <v>10</v>
       </c>
-      <c r="B17" s="10" t="inlineStr"/>
-      <c r="C17" s="24" t="inlineStr">
+      <c r="B17" s="40" t="inlineStr"/>
+      <c r="C17" s="41" t="inlineStr">
         <is>
           <t>Coctelería</t>
         </is>
       </c>
-      <c r="D17" s="12" t="inlineStr"/>
-      <c r="E17" s="13" t="inlineStr"/>
-      <c r="F17" s="14" t="n"/>
-      <c r="G17" s="15" t="n"/>
-    </row>
-    <row r="18"/>
+      <c r="D17" s="42" t="inlineStr"/>
+      <c r="E17" s="42" t="inlineStr"/>
+      <c r="F17" s="43" t="n"/>
+      <c r="G17" s="44" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="45" t="n"/>
+      <c r="B18" s="45" t="n"/>
+      <c r="C18" s="45" t="n"/>
+      <c r="D18" s="45" t="n"/>
+      <c r="E18" s="45" t="n"/>
+      <c r="F18" s="45" t="n"/>
+      <c r="G18" s="45" t="n"/>
+    </row>
     <row r="19">
-      <c r="A19" s="25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Bodega / Almacén</t>
-        </is>
-      </c>
-      <c r="B19" s="30" t="n"/>
-      <c r="C19" s="30" t="n"/>
-      <c r="D19" s="30" t="n"/>
-      <c r="E19" s="30" t="n"/>
-      <c r="F19" s="30" t="n"/>
-      <c r="G19" s="31" t="n"/>
+      <c r="A19" s="50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Bodega / Almacén — escribe aquí abajo tus tareas</t>
+        </is>
+      </c>
+      <c r="B19" s="37" t="n"/>
+      <c r="C19" s="37" t="n"/>
+      <c r="D19" s="37" t="n"/>
+      <c r="E19" s="37" t="n"/>
+      <c r="F19" s="37" t="n"/>
+      <c r="G19" s="38" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="32" t="n">
+      <c r="A20" s="39" t="n">
         <v>11</v>
       </c>
-      <c r="B20" s="10" t="inlineStr"/>
-      <c r="C20" s="27" t="inlineStr">
+      <c r="B20" s="40" t="inlineStr"/>
+      <c r="C20" s="41" t="inlineStr">
         <is>
           <t>Bodega</t>
         </is>
       </c>
-      <c r="D20" s="12" t="inlineStr"/>
-      <c r="E20" s="13" t="inlineStr"/>
-      <c r="F20" s="14" t="n"/>
-      <c r="G20" s="15" t="n"/>
+      <c r="D20" s="42" t="inlineStr">
+        <is>
+          <t>(Responsable)</t>
+        </is>
+      </c>
+      <c r="E20" s="42" t="inlineStr"/>
+      <c r="F20" s="43" t="n"/>
+      <c r="G20" s="44" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="32" t="n">
+      <c r="A21" s="39" t="n">
         <v>12</v>
       </c>
-      <c r="B21" s="10" t="inlineStr"/>
-      <c r="C21" s="27" t="inlineStr">
+      <c r="B21" s="40" t="inlineStr"/>
+      <c r="C21" s="41" t="inlineStr">
         <is>
           <t>Bodega</t>
         </is>
       </c>
-      <c r="D21" s="12" t="inlineStr"/>
-      <c r="E21" s="13" t="inlineStr"/>
-      <c r="F21" s="14" t="n"/>
-      <c r="G21" s="15" t="n"/>
+      <c r="D21" s="42" t="inlineStr"/>
+      <c r="E21" s="42" t="inlineStr"/>
+      <c r="F21" s="43" t="n"/>
+      <c r="G21" s="44" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="32" t="n">
+      <c r="A22" s="39" t="n">
         <v>13</v>
       </c>
-      <c r="B22" s="10" t="inlineStr"/>
-      <c r="C22" s="27" t="inlineStr">
+      <c r="B22" s="40" t="inlineStr"/>
+      <c r="C22" s="41" t="inlineStr">
         <is>
           <t>Bodega</t>
         </is>
       </c>
-      <c r="D22" s="12" t="inlineStr"/>
-      <c r="E22" s="13" t="inlineStr"/>
-      <c r="F22" s="14" t="n"/>
-      <c r="G22" s="15" t="n"/>
+      <c r="D22" s="42" t="inlineStr"/>
+      <c r="E22" s="42" t="inlineStr"/>
+      <c r="F22" s="43" t="n"/>
+      <c r="G22" s="44" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="32" t="n">
+      <c r="A23" s="39" t="n">
         <v>14</v>
       </c>
-      <c r="B23" s="10" t="inlineStr"/>
-      <c r="C23" s="27" t="inlineStr">
+      <c r="B23" s="40" t="inlineStr"/>
+      <c r="C23" s="41" t="inlineStr">
         <is>
           <t>Bodega</t>
         </is>
       </c>
-      <c r="D23" s="12" t="inlineStr"/>
-      <c r="E23" s="13" t="inlineStr"/>
-      <c r="F23" s="14" t="n"/>
-      <c r="G23" s="15" t="n"/>
-    </row>
-    <row r="24"/>
+      <c r="D23" s="42" t="inlineStr"/>
+      <c r="E23" s="42" t="inlineStr"/>
+      <c r="F23" s="43" t="n"/>
+      <c r="G23" s="44" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="45" t="n"/>
+      <c r="B24" s="45" t="n"/>
+      <c r="C24" s="45" t="n"/>
+      <c r="D24" s="45" t="n"/>
+      <c r="E24" s="45" t="n"/>
+      <c r="F24" s="45" t="n"/>
+      <c r="G24" s="45" t="n"/>
+    </row>
     <row r="25">
-      <c r="A25" s="28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Terraza</t>
-        </is>
-      </c>
-      <c r="B25" s="30" t="n"/>
-      <c r="C25" s="30" t="n"/>
-      <c r="D25" s="30" t="n"/>
-      <c r="E25" s="30" t="n"/>
-      <c r="F25" s="30" t="n"/>
-      <c r="G25" s="31" t="n"/>
+      <c r="A25" s="51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Terraza — escribe aquí abajo tus tareas</t>
+        </is>
+      </c>
+      <c r="B25" s="37" t="n"/>
+      <c r="C25" s="37" t="n"/>
+      <c r="D25" s="37" t="n"/>
+      <c r="E25" s="37" t="n"/>
+      <c r="F25" s="37" t="n"/>
+      <c r="G25" s="38" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="32" t="n">
+      <c r="A26" s="39" t="n">
         <v>15</v>
       </c>
-      <c r="B26" s="10" t="inlineStr"/>
-      <c r="C26" s="29" t="inlineStr">
+      <c r="B26" s="40" t="inlineStr"/>
+      <c r="C26" s="41" t="inlineStr">
         <is>
           <t>Terraza</t>
         </is>
       </c>
-      <c r="D26" s="12" t="inlineStr"/>
-      <c r="E26" s="13" t="inlineStr"/>
-      <c r="F26" s="14" t="n"/>
-      <c r="G26" s="15" t="n"/>
+      <c r="D26" s="42" t="inlineStr">
+        <is>
+          <t>(Responsable)</t>
+        </is>
+      </c>
+      <c r="E26" s="42" t="inlineStr"/>
+      <c r="F26" s="43" t="n"/>
+      <c r="G26" s="44" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="32" t="n">
+      <c r="A27" s="39" t="n">
         <v>16</v>
       </c>
-      <c r="B27" s="10" t="inlineStr"/>
-      <c r="C27" s="29" t="inlineStr">
+      <c r="B27" s="40" t="inlineStr"/>
+      <c r="C27" s="41" t="inlineStr">
         <is>
           <t>Terraza</t>
         </is>
       </c>
-      <c r="D27" s="12" t="inlineStr"/>
-      <c r="E27" s="13" t="inlineStr"/>
-      <c r="F27" s="14" t="n"/>
-      <c r="G27" s="15" t="n"/>
+      <c r="D27" s="42" t="inlineStr"/>
+      <c r="E27" s="42" t="inlineStr"/>
+      <c r="F27" s="43" t="n"/>
+      <c r="G27" s="44" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="32" t="n">
+      <c r="A28" s="39" t="n">
         <v>17</v>
       </c>
-      <c r="B28" s="10" t="inlineStr"/>
-      <c r="C28" s="29" t="inlineStr">
+      <c r="B28" s="40" t="inlineStr"/>
+      <c r="C28" s="41" t="inlineStr">
         <is>
           <t>Terraza</t>
         </is>
       </c>
-      <c r="D28" s="12" t="inlineStr"/>
-      <c r="E28" s="13" t="inlineStr"/>
-      <c r="F28" s="14" t="n"/>
-      <c r="G28" s="15" t="n"/>
+      <c r="D28" s="42" t="inlineStr"/>
+      <c r="E28" s="42" t="inlineStr"/>
+      <c r="F28" s="43" t="n"/>
+      <c r="G28" s="44" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="32" t="n">
+      <c r="A29" s="39" t="n">
         <v>18</v>
       </c>
-      <c r="B29" s="10" t="inlineStr"/>
-      <c r="C29" s="29" t="inlineStr">
+      <c r="B29" s="40" t="inlineStr"/>
+      <c r="C29" s="41" t="inlineStr">
         <is>
           <t>Terraza</t>
         </is>
       </c>
-      <c r="D29" s="12" t="inlineStr"/>
-      <c r="E29" s="13" t="inlineStr"/>
-      <c r="F29" s="14" t="n"/>
-      <c r="G29" s="15" t="n"/>
-    </row>
-    <row r="30"/>
-    <row r="31"/>
+      <c r="D29" s="42" t="inlineStr"/>
+      <c r="E29" s="42" t="inlineStr"/>
+      <c r="F29" s="43" t="n"/>
+      <c r="G29" s="44" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="46" t="n"/>
+      <c r="B30" s="40" t="n"/>
+      <c r="C30" s="41" t="n"/>
+      <c r="D30" s="42" t="n"/>
+      <c r="E30" s="42" t="n"/>
+      <c r="F30" s="43" t="n"/>
+      <c r="G30" s="44" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="46" t="n"/>
+      <c r="B31" s="40" t="n"/>
+      <c r="C31" s="41" t="n"/>
+      <c r="D31" s="42" t="n"/>
+      <c r="E31" s="42" t="n"/>
+      <c r="F31" s="43" t="n"/>
+      <c r="G31" s="44" t="n"/>
+    </row>
     <row r="32">
-      <c r="A32" s="16" t="inlineStr">
-        <is>
-          <t>Tareas completadas:</t>
-        </is>
-      </c>
-      <c r="D32" s="16">
-        <f>COUNTIF(F5:F30,"✓")</f>
-        <v>0.0</v>
-      </c>
-      <c r="E32" s="17" t="inlineStr">
-        <is>
-          <t>de</t>
-        </is>
-      </c>
-      <c r="F32" s="16" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="33"/>
+      <c r="A32" s="46" t="n"/>
+      <c r="B32" s="40" t="n"/>
+      <c r="C32" s="41" t="n"/>
+      <c r="D32" s="42" t="n"/>
+      <c r="E32" s="42" t="n"/>
+      <c r="F32" s="43" t="n"/>
+      <c r="G32" s="44" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="46" t="n"/>
+      <c r="B33" s="40" t="n"/>
+      <c r="C33" s="41" t="n"/>
+      <c r="D33" s="42" t="n"/>
+      <c r="E33" s="42" t="n"/>
+      <c r="F33" s="43" t="n"/>
+      <c r="G33" s="44" t="n"/>
+    </row>
     <row r="34">
-      <c r="A34" s="16" t="inlineStr">
-        <is>
-          <t>Verificado por:</t>
-        </is>
-      </c>
-      <c r="B34" s="15" t="n"/>
-      <c r="C34" s="30" t="n"/>
-      <c r="D34" s="31" t="n"/>
-      <c r="E34" s="16" t="inlineStr">
-        <is>
-          <t>Firma:</t>
-        </is>
-      </c>
-      <c r="F34" s="15" t="n"/>
-      <c r="G34" s="31" t="n"/>
+      <c r="A34" s="46" t="n"/>
+      <c r="B34" s="40" t="n"/>
+      <c r="C34" s="41" t="n"/>
+      <c r="D34" s="42" t="n"/>
+      <c r="E34" s="42" t="n"/>
+      <c r="F34" s="43" t="n"/>
+      <c r="G34" s="44" t="n"/>
     </row>
     <row r="35"/>
     <row r="36">
-      <c r="A36" s="18" t="inlineStr">
+      <c r="A36" s="16" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="D36" s="16">
+        <f>COUNTIFS(B5:B34,"?*",F5:F34,"✓")</f>
+        <v>0.0</v>
+      </c>
+      <c r="E36" s="17" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="F36" s="16">
+        <f>COUNTIF(B5:B34,"?*")-COUNTIF(F5:F34,"N/A")</f>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="37"/>
+    <row r="38">
+      <c r="A38" s="16" t="inlineStr">
+        <is>
+          <t>Verificado por:</t>
+        </is>
+      </c>
+      <c r="B38" s="47" t="n"/>
+      <c r="C38" s="30" t="n"/>
+      <c r="D38" s="31" t="n"/>
+      <c r="E38" s="16" t="inlineStr">
+        <is>
+          <t>Firma:</t>
+        </is>
+      </c>
+      <c r="F38" s="47" t="n"/>
+      <c r="G38" s="31" t="n"/>
+    </row>
+    <row r="39"/>
+    <row r="40">
+      <c r="A40" s="18" t="inlineStr">
         <is>
           <t>— Kit de Tareas Recurrentes · Bar / Cocktails · AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
   <mergeCells count="9">
     <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A19:G19"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A19:G19"/>
-    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="B38:D38"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="F34:G34"/>
     <mergeCell ref="A25:G25"/>
-    <mergeCell ref="B34:D34"/>
     <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A36:C36"/>
+    <mergeCell ref="F38:G38"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:G30">
+  <conditionalFormatting sqref="A5:G34">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$F5="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F10 F13 F14 F15 F16 F17 F20 F21 F22 F23 F26 F27 F28 F29 F30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F13 F14 F15 F16 F17 F20 F21 F22 F23 F26 F27 F28 F29 F30 F31 F32 F33 F34" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." type="list" errorStyle="stop">
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1705,7 +2006,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1727,7 +2028,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Fecha: ___/___/______    Turno: ☐ Mañana  ☐ Tarde  ☐ Noche    Responsable turno: _________________________</t>
+          <t>Fecha: ___/___/______    Responsable: _________________________</t>
         </is>
       </c>
     </row>
@@ -1770,366 +2071,436 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Head Bartender</t>
-        </is>
-      </c>
-      <c r="B5" s="30" t="n"/>
-      <c r="C5" s="30" t="n"/>
-      <c r="D5" s="30" t="n"/>
-      <c r="E5" s="30" t="n"/>
-      <c r="F5" s="30" t="n"/>
-      <c r="G5" s="31" t="n"/>
+      <c r="A5" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Head Bartender — escribe aquí abajo tus tareas</t>
+        </is>
+      </c>
+      <c r="B5" s="37" t="n"/>
+      <c r="C5" s="37" t="n"/>
+      <c r="D5" s="37" t="n"/>
+      <c r="E5" s="37" t="n"/>
+      <c r="F5" s="37" t="n"/>
+      <c r="G5" s="38" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="32" t="n">
+      <c r="A6" s="39" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="10" t="inlineStr"/>
-      <c r="C6" s="11" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="D6" s="12" t="inlineStr"/>
-      <c r="E6" s="13" t="inlineStr"/>
-      <c r="F6" s="14" t="n"/>
-      <c r="G6" s="15" t="n"/>
+      <c r="B6" s="40" t="inlineStr"/>
+      <c r="C6" s="41" t="n"/>
+      <c r="D6" s="42" t="inlineStr">
+        <is>
+          <t>Head Bartender</t>
+        </is>
+      </c>
+      <c r="E6" s="42" t="inlineStr"/>
+      <c r="F6" s="43" t="n"/>
+      <c r="G6" s="44" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="32" t="n">
+      <c r="A7" s="39" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="10" t="inlineStr"/>
-      <c r="C7" s="11" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="D7" s="12" t="inlineStr"/>
-      <c r="E7" s="13" t="inlineStr"/>
-      <c r="F7" s="14" t="n"/>
-      <c r="G7" s="15" t="n"/>
+      <c r="B7" s="40" t="inlineStr"/>
+      <c r="C7" s="41" t="n"/>
+      <c r="D7" s="42" t="inlineStr">
+        <is>
+          <t>Head Bartender</t>
+        </is>
+      </c>
+      <c r="E7" s="42" t="inlineStr"/>
+      <c r="F7" s="43" t="n"/>
+      <c r="G7" s="44" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="32" t="n">
+      <c r="A8" s="39" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="10" t="inlineStr"/>
-      <c r="C8" s="11" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="D8" s="12" t="inlineStr"/>
-      <c r="E8" s="13" t="inlineStr"/>
-      <c r="F8" s="14" t="n"/>
-      <c r="G8" s="15" t="n"/>
+      <c r="B8" s="40" t="inlineStr"/>
+      <c r="C8" s="41" t="n"/>
+      <c r="D8" s="42" t="inlineStr">
+        <is>
+          <t>Head Bartender</t>
+        </is>
+      </c>
+      <c r="E8" s="42" t="inlineStr"/>
+      <c r="F8" s="43" t="n"/>
+      <c r="G8" s="44" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="32" t="n">
+      <c r="A9" s="39" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="10" t="inlineStr"/>
-      <c r="C9" s="11" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="D9" s="12" t="inlineStr"/>
-      <c r="E9" s="13" t="inlineStr"/>
-      <c r="F9" s="14" t="n"/>
-      <c r="G9" s="15" t="n"/>
-    </row>
-    <row r="10"/>
+      <c r="B9" s="40" t="inlineStr"/>
+      <c r="C9" s="41" t="n"/>
+      <c r="D9" s="42" t="inlineStr">
+        <is>
+          <t>Head Bartender</t>
+        </is>
+      </c>
+      <c r="E9" s="42" t="inlineStr"/>
+      <c r="F9" s="43" t="n"/>
+      <c r="G9" s="44" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="45" t="n"/>
+      <c r="B10" s="45" t="n"/>
+      <c r="C10" s="45" t="n"/>
+      <c r="D10" s="45" t="n"/>
+      <c r="E10" s="45" t="n"/>
+      <c r="F10" s="45" t="n"/>
+      <c r="G10" s="45" t="n"/>
+    </row>
     <row r="11">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Bartender</t>
-        </is>
-      </c>
-      <c r="B11" s="30" t="n"/>
-      <c r="C11" s="30" t="n"/>
-      <c r="D11" s="30" t="n"/>
-      <c r="E11" s="30" t="n"/>
-      <c r="F11" s="30" t="n"/>
-      <c r="G11" s="31" t="n"/>
+      <c r="A11" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Bartender — escribe aquí abajo tus tareas</t>
+        </is>
+      </c>
+      <c r="B11" s="37" t="n"/>
+      <c r="C11" s="37" t="n"/>
+      <c r="D11" s="37" t="n"/>
+      <c r="E11" s="37" t="n"/>
+      <c r="F11" s="37" t="n"/>
+      <c r="G11" s="38" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="32" t="n">
+      <c r="A12" s="39" t="n">
         <v>5</v>
       </c>
-      <c r="B12" s="10" t="inlineStr"/>
-      <c r="C12" s="11" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="D12" s="12" t="inlineStr"/>
-      <c r="E12" s="13" t="inlineStr"/>
-      <c r="F12" s="14" t="n"/>
-      <c r="G12" s="15" t="n"/>
+      <c r="B12" s="40" t="inlineStr"/>
+      <c r="C12" s="41" t="n"/>
+      <c r="D12" s="42" t="inlineStr">
+        <is>
+          <t>Bartender</t>
+        </is>
+      </c>
+      <c r="E12" s="42" t="inlineStr"/>
+      <c r="F12" s="43" t="n"/>
+      <c r="G12" s="44" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="32" t="n">
+      <c r="A13" s="39" t="n">
         <v>6</v>
       </c>
-      <c r="B13" s="10" t="inlineStr"/>
-      <c r="C13" s="11" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="D13" s="12" t="inlineStr"/>
-      <c r="E13" s="13" t="inlineStr"/>
-      <c r="F13" s="14" t="n"/>
-      <c r="G13" s="15" t="n"/>
+      <c r="B13" s="40" t="inlineStr"/>
+      <c r="C13" s="41" t="n"/>
+      <c r="D13" s="42" t="inlineStr">
+        <is>
+          <t>Bartender</t>
+        </is>
+      </c>
+      <c r="E13" s="42" t="inlineStr"/>
+      <c r="F13" s="43" t="n"/>
+      <c r="G13" s="44" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="32" t="n">
+      <c r="A14" s="39" t="n">
         <v>7</v>
       </c>
-      <c r="B14" s="10" t="inlineStr"/>
-      <c r="C14" s="11" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="D14" s="12" t="inlineStr"/>
-      <c r="E14" s="13" t="inlineStr"/>
-      <c r="F14" s="14" t="n"/>
-      <c r="G14" s="15" t="n"/>
+      <c r="B14" s="40" t="inlineStr"/>
+      <c r="C14" s="41" t="n"/>
+      <c r="D14" s="42" t="inlineStr">
+        <is>
+          <t>Bartender</t>
+        </is>
+      </c>
+      <c r="E14" s="42" t="inlineStr"/>
+      <c r="F14" s="43" t="n"/>
+      <c r="G14" s="44" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="32" t="n">
+      <c r="A15" s="39" t="n">
         <v>8</v>
       </c>
-      <c r="B15" s="10" t="inlineStr"/>
-      <c r="C15" s="11" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="D15" s="12" t="inlineStr"/>
-      <c r="E15" s="13" t="inlineStr"/>
-      <c r="F15" s="14" t="n"/>
-      <c r="G15" s="15" t="n"/>
-    </row>
-    <row r="16"/>
+      <c r="B15" s="40" t="inlineStr"/>
+      <c r="C15" s="41" t="n"/>
+      <c r="D15" s="42" t="inlineStr">
+        <is>
+          <t>Bartender</t>
+        </is>
+      </c>
+      <c r="E15" s="42" t="inlineStr"/>
+      <c r="F15" s="43" t="n"/>
+      <c r="G15" s="44" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="45" t="n"/>
+      <c r="B16" s="45" t="n"/>
+      <c r="C16" s="45" t="n"/>
+      <c r="D16" s="45" t="n"/>
+      <c r="E16" s="45" t="n"/>
+      <c r="F16" s="45" t="n"/>
+      <c r="G16" s="45" t="n"/>
+    </row>
     <row r="17">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Barback</t>
-        </is>
-      </c>
-      <c r="B17" s="30" t="n"/>
-      <c r="C17" s="30" t="n"/>
-      <c r="D17" s="30" t="n"/>
-      <c r="E17" s="30" t="n"/>
-      <c r="F17" s="30" t="n"/>
-      <c r="G17" s="31" t="n"/>
+      <c r="A17" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Barback — escribe aquí abajo tus tareas</t>
+        </is>
+      </c>
+      <c r="B17" s="37" t="n"/>
+      <c r="C17" s="37" t="n"/>
+      <c r="D17" s="37" t="n"/>
+      <c r="E17" s="37" t="n"/>
+      <c r="F17" s="37" t="n"/>
+      <c r="G17" s="38" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="32" t="n">
+      <c r="A18" s="39" t="n">
         <v>9</v>
       </c>
-      <c r="B18" s="10" t="inlineStr"/>
-      <c r="C18" s="11" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="D18" s="12" t="inlineStr"/>
-      <c r="E18" s="13" t="inlineStr"/>
-      <c r="F18" s="14" t="n"/>
-      <c r="G18" s="15" t="n"/>
+      <c r="B18" s="40" t="inlineStr"/>
+      <c r="C18" s="41" t="n"/>
+      <c r="D18" s="42" t="inlineStr">
+        <is>
+          <t>Barback</t>
+        </is>
+      </c>
+      <c r="E18" s="42" t="inlineStr"/>
+      <c r="F18" s="43" t="n"/>
+      <c r="G18" s="44" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="32" t="n">
+      <c r="A19" s="39" t="n">
         <v>10</v>
       </c>
-      <c r="B19" s="10" t="inlineStr"/>
-      <c r="C19" s="11" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="D19" s="12" t="inlineStr"/>
-      <c r="E19" s="13" t="inlineStr"/>
-      <c r="F19" s="14" t="n"/>
-      <c r="G19" s="15" t="n"/>
+      <c r="B19" s="40" t="inlineStr"/>
+      <c r="C19" s="41" t="n"/>
+      <c r="D19" s="42" t="inlineStr">
+        <is>
+          <t>Barback</t>
+        </is>
+      </c>
+      <c r="E19" s="42" t="inlineStr"/>
+      <c r="F19" s="43" t="n"/>
+      <c r="G19" s="44" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="32" t="n">
+      <c r="A20" s="39" t="n">
         <v>11</v>
       </c>
-      <c r="B20" s="10" t="inlineStr"/>
-      <c r="C20" s="11" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="D20" s="12" t="inlineStr"/>
-      <c r="E20" s="13" t="inlineStr"/>
-      <c r="F20" s="14" t="n"/>
-      <c r="G20" s="15" t="n"/>
+      <c r="B20" s="40" t="inlineStr"/>
+      <c r="C20" s="41" t="n"/>
+      <c r="D20" s="42" t="inlineStr">
+        <is>
+          <t>Barback</t>
+        </is>
+      </c>
+      <c r="E20" s="42" t="inlineStr"/>
+      <c r="F20" s="43" t="n"/>
+      <c r="G20" s="44" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="32" t="n">
+      <c r="A21" s="39" t="n">
         <v>12</v>
       </c>
-      <c r="B21" s="10" t="inlineStr"/>
-      <c r="C21" s="11" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="D21" s="12" t="inlineStr"/>
-      <c r="E21" s="13" t="inlineStr"/>
-      <c r="F21" s="14" t="n"/>
-      <c r="G21" s="15" t="n"/>
-    </row>
-    <row r="22"/>
+      <c r="B21" s="40" t="inlineStr"/>
+      <c r="C21" s="41" t="n"/>
+      <c r="D21" s="42" t="inlineStr">
+        <is>
+          <t>Barback</t>
+        </is>
+      </c>
+      <c r="E21" s="42" t="inlineStr"/>
+      <c r="F21" s="43" t="n"/>
+      <c r="G21" s="44" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="45" t="n"/>
+      <c r="B22" s="45" t="n"/>
+      <c r="C22" s="45" t="n"/>
+      <c r="D22" s="45" t="n"/>
+      <c r="E22" s="45" t="n"/>
+      <c r="F22" s="45" t="n"/>
+      <c r="G22" s="45" t="n"/>
+    </row>
     <row r="23">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Camarero</t>
-        </is>
-      </c>
-      <c r="B23" s="30" t="n"/>
-      <c r="C23" s="30" t="n"/>
-      <c r="D23" s="30" t="n"/>
-      <c r="E23" s="30" t="n"/>
-      <c r="F23" s="30" t="n"/>
-      <c r="G23" s="31" t="n"/>
+      <c r="A23" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Camarero — escribe aquí abajo tus tareas</t>
+        </is>
+      </c>
+      <c r="B23" s="37" t="n"/>
+      <c r="C23" s="37" t="n"/>
+      <c r="D23" s="37" t="n"/>
+      <c r="E23" s="37" t="n"/>
+      <c r="F23" s="37" t="n"/>
+      <c r="G23" s="38" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="32" t="n">
+      <c r="A24" s="39" t="n">
         <v>13</v>
       </c>
-      <c r="B24" s="10" t="inlineStr"/>
-      <c r="C24" s="11" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="D24" s="12" t="inlineStr"/>
-      <c r="E24" s="13" t="inlineStr"/>
-      <c r="F24" s="14" t="n"/>
-      <c r="G24" s="15" t="n"/>
+      <c r="B24" s="40" t="inlineStr"/>
+      <c r="C24" s="41" t="n"/>
+      <c r="D24" s="42" t="inlineStr">
+        <is>
+          <t>Camarero</t>
+        </is>
+      </c>
+      <c r="E24" s="42" t="inlineStr"/>
+      <c r="F24" s="43" t="n"/>
+      <c r="G24" s="44" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="32" t="n">
+      <c r="A25" s="39" t="n">
         <v>14</v>
       </c>
-      <c r="B25" s="10" t="inlineStr"/>
-      <c r="C25" s="11" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="D25" s="12" t="inlineStr"/>
-      <c r="E25" s="13" t="inlineStr"/>
-      <c r="F25" s="14" t="n"/>
-      <c r="G25" s="15" t="n"/>
+      <c r="B25" s="40" t="inlineStr"/>
+      <c r="C25" s="41" t="n"/>
+      <c r="D25" s="42" t="inlineStr">
+        <is>
+          <t>Camarero</t>
+        </is>
+      </c>
+      <c r="E25" s="42" t="inlineStr"/>
+      <c r="F25" s="43" t="n"/>
+      <c r="G25" s="44" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="32" t="n">
+      <c r="A26" s="39" t="n">
         <v>15</v>
       </c>
-      <c r="B26" s="10" t="inlineStr"/>
-      <c r="C26" s="11" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="D26" s="12" t="inlineStr"/>
-      <c r="E26" s="13" t="inlineStr"/>
-      <c r="F26" s="14" t="n"/>
-      <c r="G26" s="15" t="n"/>
+      <c r="B26" s="40" t="inlineStr"/>
+      <c r="C26" s="41" t="n"/>
+      <c r="D26" s="42" t="inlineStr">
+        <is>
+          <t>Camarero</t>
+        </is>
+      </c>
+      <c r="E26" s="42" t="inlineStr"/>
+      <c r="F26" s="43" t="n"/>
+      <c r="G26" s="44" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="32" t="n">
+      <c r="A27" s="39" t="n">
         <v>16</v>
       </c>
-      <c r="B27" s="10" t="inlineStr"/>
-      <c r="C27" s="11" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="D27" s="12" t="inlineStr"/>
-      <c r="E27" s="13" t="inlineStr"/>
-      <c r="F27" s="14" t="n"/>
-      <c r="G27" s="15" t="n"/>
-    </row>
-    <row r="28"/>
-    <row r="29"/>
+      <c r="B27" s="40" t="inlineStr"/>
+      <c r="C27" s="41" t="n"/>
+      <c r="D27" s="42" t="inlineStr">
+        <is>
+          <t>Camarero</t>
+        </is>
+      </c>
+      <c r="E27" s="42" t="inlineStr"/>
+      <c r="F27" s="43" t="n"/>
+      <c r="G27" s="44" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="46" t="n"/>
+      <c r="B28" s="40" t="n"/>
+      <c r="C28" s="41" t="n"/>
+      <c r="D28" s="42" t="n"/>
+      <c r="E28" s="42" t="n"/>
+      <c r="F28" s="43" t="n"/>
+      <c r="G28" s="44" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="46" t="n"/>
+      <c r="B29" s="40" t="n"/>
+      <c r="C29" s="41" t="n"/>
+      <c r="D29" s="42" t="n"/>
+      <c r="E29" s="42" t="n"/>
+      <c r="F29" s="43" t="n"/>
+      <c r="G29" s="44" t="n"/>
+    </row>
     <row r="30">
-      <c r="A30" s="16" t="inlineStr">
-        <is>
-          <t>Tareas completadas:</t>
-        </is>
-      </c>
-      <c r="D30" s="16">
-        <f>COUNTIF(F5:F28,"✓")</f>
-        <v>0.0</v>
-      </c>
-      <c r="E30" s="17" t="inlineStr">
-        <is>
-          <t>de</t>
-        </is>
-      </c>
-      <c r="F30" s="16" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="31"/>
+      <c r="A30" s="46" t="n"/>
+      <c r="B30" s="40" t="n"/>
+      <c r="C30" s="41" t="n"/>
+      <c r="D30" s="42" t="n"/>
+      <c r="E30" s="42" t="n"/>
+      <c r="F30" s="43" t="n"/>
+      <c r="G30" s="44" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="46" t="n"/>
+      <c r="B31" s="40" t="n"/>
+      <c r="C31" s="41" t="n"/>
+      <c r="D31" s="42" t="n"/>
+      <c r="E31" s="42" t="n"/>
+      <c r="F31" s="43" t="n"/>
+      <c r="G31" s="44" t="n"/>
+    </row>
     <row r="32">
-      <c r="A32" s="16" t="inlineStr">
-        <is>
-          <t>Verificado por:</t>
-        </is>
-      </c>
-      <c r="B32" s="15" t="n"/>
-      <c r="C32" s="30" t="n"/>
-      <c r="D32" s="31" t="n"/>
-      <c r="E32" s="16" t="inlineStr">
-        <is>
-          <t>Firma:</t>
-        </is>
-      </c>
-      <c r="F32" s="15" t="n"/>
-      <c r="G32" s="31" t="n"/>
+      <c r="A32" s="46" t="n"/>
+      <c r="B32" s="40" t="n"/>
+      <c r="C32" s="41" t="n"/>
+      <c r="D32" s="42" t="n"/>
+      <c r="E32" s="42" t="n"/>
+      <c r="F32" s="43" t="n"/>
+      <c r="G32" s="44" t="n"/>
     </row>
     <row r="33"/>
     <row r="34">
-      <c r="A34" s="18" t="inlineStr">
+      <c r="A34" s="16" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="D34" s="16">
+        <f>COUNTIFS(B5:B32,"?*",F5:F32,"✓")</f>
+        <v>0.0</v>
+      </c>
+      <c r="E34" s="17" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="F34" s="16">
+        <f>COUNTIF(B5:B32,"?*")-COUNTIF(F5:F32,"N/A")</f>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="35"/>
+    <row r="36">
+      <c r="A36" s="16" t="inlineStr">
+        <is>
+          <t>Verificado por:</t>
+        </is>
+      </c>
+      <c r="B36" s="47" t="n"/>
+      <c r="C36" s="30" t="n"/>
+      <c r="D36" s="31" t="n"/>
+      <c r="E36" s="16" t="inlineStr">
+        <is>
+          <t>Firma:</t>
+        </is>
+      </c>
+      <c r="F36" s="47" t="n"/>
+      <c r="G36" s="31" t="n"/>
+    </row>
+    <row r="37"/>
+    <row r="38">
+      <c r="A38" s="18" t="inlineStr">
         <is>
           <t>— Kit de Tareas Recurrentes · Bar / Cocktails · AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
   <mergeCells count="9">
-    <mergeCell ref="F32:G32"/>
+    <mergeCell ref="A17:G17"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A17:G17"/>
-    <mergeCell ref="B32:D32"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="A11:G11"/>
     <mergeCell ref="A23:G23"/>
+    <mergeCell ref="F36:G36"/>
     <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="B36:D36"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:G28">
+  <conditionalFormatting sqref="A5:G32">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$F5="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F12 F13 F14 F15 F18 F19 F20 F21 F24 F25 F26 F27 F28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F6 F7 F8 F9 F12 F13 F14 F15 F18 F19 F20 F21 F24 F25 F26 F27 F28 F29 F30 F31 F32" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." type="list" errorStyle="stop">
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
